--- a/Calculos_de_Dado/PT_Matriz_de_Riscos_Motiva.xlsx
+++ b/Calculos_de_Dado/PT_Matriz_de_Riscos_Motiva.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6723ABB0-D825-465C-B127-99F60601BC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26EAC4B9-4023-4C27-BF26-E27536C664B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Q12" sheetId="1" r:id="rId1"/>
+    <sheet name="Q16" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>Ref. PT</t>
   </si>
@@ -139,12 +140,150 @@
       <t>).</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>Ref.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tipo de Distorção</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Natureza / Descrição da Distorção</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Conta Afetada (Ativo/Passivo)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Conta Afetada (Resultado)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ajuste Proposto (R$ Mil)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>A </t>
+  </si>
+  <si>
+    <t>Factual / Julgamento </t>
+  </si>
+  <si>
+    <t>Receita de Construção (POC): O especialista de engenharia detectou que a medição de uma obra de duplicação foi antecipada para dezembro de 2025, quando só foi concluída em janeiro de 2026. A determinação do percentual de conclusão envolve julgamento, mas o erro de cut-off é um fato. </t>
+  </si>
+  <si>
+    <t>Intangível de Concessão (Maior) </t>
+  </si>
+  <si>
+    <t>Receita de Construção (Sobrestimado) </t>
+  </si>
+  <si>
+    <t>(R$ 85.000) - Reverter receita </t>
+  </si>
+  <si>
+    <t>B </t>
+  </si>
+  <si>
+    <t>Factual </t>
+  </si>
+  <si>
+    <t>Provisões Ambientais: Inspeção de um novo Termo de Compromisso (TAC) revelou que uma obrigação de reflorestamento assumida pela empresa não foi registrada na contabilidade. </t>
+  </si>
+  <si>
+    <t>Provisões P/ Contingências (Menor) </t>
+  </si>
+  <si>
+    <t>Despesa com Obrigações (Sobrestimado - não registrada) </t>
+  </si>
+  <si>
+    <t>(R$ 45.000) - Reconhecer passivo/despesa </t>
+  </si>
+  <si>
+    <t>C </t>
+  </si>
+  <si>
+    <t>Projetada </t>
+  </si>
+  <si>
+    <t>Provisão para Manutenção: Extrapolação de erros identificados na amostra de recálculo de premissas financeiras de custos futuros de manutenção em rodovias de menor porte da Motiva S.A. </t>
+  </si>
+  <si>
+    <t>Provisão para Manutenção (Menor) </t>
+  </si>
+  <si>
+    <t>Despesa de Manutenção (Sobrestimado) </t>
+  </si>
+  <si>
+    <t>(R$ 15.000) - Aumento da Provisão </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +314,19 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -184,7 +336,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -207,17 +359,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,4 +832,103 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1D5CE8A-C40C-46B7-9EC8-670A25A6448A}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="150.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="23.25">
+      <c r="A2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>